--- a/docs/业务办理流程文案_复核_小程序.xlsx
+++ b/docs/业务办理流程文案_复核_小程序.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务办理流程 · 总览" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,38 +11,197 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通用下单流程 · 页面文案" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="25">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00F4D9A6"/>
+      <color rgb="FFF4D9A6"/>
       <sz val="10.5"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="134"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <sz val="10.5"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -52,11 +210,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F1A12"/>
+        <fgColor rgb="FF1F1A12"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -66,39 +411,333 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -451,7 +1090,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -462,7 +1100,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -470,8 +1108,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="7" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
@@ -541,35 +1178,35 @@
       </c>
     </row>
     <row r="2" ht="150" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>公司名称查册 + 商标查询</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>HKD 99 / ¥ 89（券后 0 元）</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>约 1–2 个工作日出结果</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>选择项目（公司名称查册 / 商标查询）—— 下单 —— 支付 —— 去核名&amp;查商标（填写并提交）</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>注册香港公司前的名称与商标预查，顾问人工核查可用性，降低被驳回 / 侵权风险。新客赠 3 张免费券，下单可抵扣。</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>· 公司名称可用性查册（公司注册处）
 · 商标近似查询（知识产权署 IPD）
@@ -577,68 +1214,68 @@
 · 顾问人工核查 + 可用性建议报告</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>· 拟用公司名称（英文 / 繁体中文）
 · 拟查商标名称 / 图样（如需）
 · 联系邮箱</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>在香港公司注册处核查公司名称可用性，在知识产权署 IPD做商标近似查询，由顾问人工核查并给出可用性建议。查册语言只支持英文或繁体中文；名称通过后可直接进入公司注册。费用 HKD 99；新客赠 3 张免费核名券，下单时可抵扣（最多可免费办理 3 次）。</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>在香港公司注册处核查公司名称可用性，在知识产权署 IPD 做商标近似查询，由顾问人工核查并给出可用性建议。查册语言只支持英文或繁体中文；名称通过后可直接进入公司注册。费用 HKD 99；新客赠 3 张免费核名券，下单时可抵扣（最多可免费办理 3 次）。</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>下单 &amp; 支付 · 顾问人工查册 · 出核查结果</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>① 账单支付页（下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（下单✓ / 支付✓ / 办理·进行中）：核名 &amp; 商标查询已下单，点击下方开始填写。
 ③ 公司核名填写页（顶部勾选：公司名称查册 / 商标查询，可多选）
-④ 结果页「人工核名中」：我们的顾问正在香港公司注册处为你查册，大约需 1–2 天，结果将通过消息通知你。
+④ 结果页「人工核名中」：我们的顾问正在香港公司注册处为您查册，大约需 1–2 天，结果将通过消息通知您。
 ⑤ 核名 &amp; 商标查询结果页。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="150" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>新设香港本地有限公司</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>HKD 5,533 / ¥ 4,980</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>约 10 个工作日</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>公司资料 —— 成员/董事 —— 组织章程 —— 人工预审</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>10 个工作日以内</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>公司资料 —— 股东/董事 —— 组织章程 —— 人工预审</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>香港本地有限公司一站式注册，含全套证照、印章与绿盒，全程托办。</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>· 注册证书 CI ×1
 · 商业登记证 BR ×1
@@ -652,7 +1289,7 @@
 · 绿盒</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>· 董事 / 股东身份证或护照
 · 拟用公司名称（中 / 英）
@@ -661,64 +1298,64 @@
 · 注册地址（可用法定秘书地址）</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>新设香港本地有限公司，涵盖公司注册处 NNC1 递交、商业登记、章程与法团文件制作。下单后完成支付与 KYC 尽调、提交注册信息，人工预审无误后递交政府审批，通过即签发 CI + BR 并交付全套绿盒资料。</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>【公司资料页】拟用公司全名（繁体中文）· 拟用公司全名（英文）· 拟经营业务性质（HSIC）· 注册办事处地址（单选：填写秘书公司地址 / 需要租赁办公室）· 公司电邮 · 股本（股份类别/货币/发行股数/认购股本）
-【成员/董事页】身份（创办成员 / 董事，可多选）· 证件类型（香港身份证 / 护照 / 其他）+ 证件上传（OCR 自动带出姓名、证件号）· 通讯地址（香港/非香港，非香港显示国家地区默认中国）· 常驻地址（默认同通讯地址）· 联络电邮
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>【公司资料页】拟用公司全名（繁体中文）· 拟用公司全名（英文）· 拟经营业务性质（HSIC·底部弹窗）· 注册办事处地址（单选：填写秘书公司地址 / 需要租赁办公室）· 公司电邮 · 股本（股份类别默认普通股/货币/发行股数/认购股本）
+【股东/董事页】类型（自然人/法人，先选类型再选身份）· 身份（股东 / 董事，可多选）· 证件类型（香港身份证 / 护照 / 其他）+ 证件上传（OCR 自动带出姓名、证件号）+ 手持证件照片（人证一致）· 通讯地址（香港/非香港，非香港显示国家地区默认中国）· 常驻地址（默认同通讯地址）· 联络电邮
 【组织章程页】样本 A（简化格式·推荐）/ 样本 B · 章程语言（英文 / 繁体中文）
 【人工预审页】资料汇总 + NNC1 法团成立表格预览</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>支付 · KYC 认证 · 提交注册信息 · 人工预审 · 政府审批 · 交付 CI / BR</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>支付 · KYC 认证 · 提交注册信息 · 预审与文件编制 · 文件签字 · 递交注册处 · 交付 CI / BR</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（下单✓ / 支付✓ / 办理·进行中）· 两个豆腐块：完成 KYC 实名认证 / 提交公司注册信息
-③ 提交注册信息（公司资料 / 成员董事 / 组织章程 / 人工预审 四页）
-④ 结果页「业务办理中」：人工预审通过后，顾问将线下递交 NNC1 表至香港公司注册处；交表后约 1 周可领取 CI / BR 正本。
-⑤ 完成页「公司注册完成」：TimeLeap Limited 已成功注册，CI 与 BR 已签发，交付物已送达交付物中心。</t>
+③ 提交注册信息（公司资料 / 股东董事 / 组织章程 / 人工预审 四页）
+④ 结果页「业务办理中」：人工预审通过后，顾问将编制 NNC1 表格并安排董事 / 股东文件签字，签妥后递交香港公司注册处；签发 CI + BR 后快递寄出。
+⑤ 完成页「公司注册完成」：TimeLeap Limited 已成功注册，CI 与 BR 已签发，交付物已快递寄出（快递单号 SF1234567890）。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>年审服务</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>HKD 4,422 / ¥ 3,980</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>年费 · NAR1 须成立周年日起 42 天内递交</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>年费 · NAR1 须成立周年日起 42 天内递交 · 约 10 个工作日出件</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>支付 / 续费 —— 信息核对 —— 编制 NAR1 —— 递交注册处 —— 完结</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>法定秘书 + 注册地址 + 周年申报 NAR1 的年度合规打包服务。</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>· 担任法定公司秘书
 · 维护法定登记册
@@ -727,19 +1364,19 @@
 · 接收 / 转发政府信件</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>· 公司名称 / 商业登记号 BR
 · 公司成立周年日
 · 董事 / 股东最新资料（如有变动）</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>公司注册处年度合规打包：担任法定公司秘书、维护法定登记册、编制并递交周年申报表 NAR1，并提供香港注册地址与政府信件接收 / 转发。NAR1 逾期政府罚款递增。注意：这是公司注册处的年度合规，与税务局的审计 / 利得税报税（见「审计·含理账」）不同。</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 公司名称
@@ -748,51 +1385,51 @@
 · 财政年度结算日（如 03-31）</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>支付 / 续费 · 信息核对 · 编制 NAR1 · 递交注册处 · 完结</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>支付 / 续费 · 信息核对 · 编制 NAR1 · 递交注册处 · 交付 NAR1 与 BR</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>审计（含理账）</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>按年度办理 · 时效视资料完整度</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>报价确认 —— 资料收集 —— 理账 + 财报 —— 独立审计 —— 利得税 PTR —— 提交 IRD</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>理账 + 财务报表 + 独立审计 + 利得税报税表 PTR，面向税务局 IRD。</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>· 日常记账与凭证整理（理账）
 · 财务报表编制
@@ -800,7 +1437,7 @@
 · 利得税报税表 PTR 编制与提交</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>· 全年银行流水 / 对账单
 · 销售与采购单据 / 发票
@@ -808,58 +1445,58 @@
 · 上年度审计报告（如有）</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>审计（含理账）：日常记账与凭证整理 → 财务报表编制 → 执业会计师（CPA）独立审计 → 利得税报税表 PTR 编制与提交（IRD）。跨境电商可导入平台账单批量入账。按年度银行流水总额 / 交易笔数报价（面议）。</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>（面议服务：无需在线填写，预约后由顾问对接）</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>报价确认 · 资料收集 · 理账 + 财报 · 独立审计 · 利得税 PTR · 提交 IRD</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>① 预约咨询二次确认（底部弹窗）：你正在预约 审计（含理账）。确认后，专属顾问将在 24 小时内与你联系并提供报价方案。
-② 预约成功页（顶部：提交预约✓ / 顾问联系 / 报价确认）：已收到你的「审计（含理账）」预约，专属顾问将在 24 小时内与你联系并提供报价方案。可在「我的订单」查看进度。</t>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>报价确认 · 资料收集 · 理账 + 财报 · 独立审计 · 利得税报税表 PTR · 提交 IRD · 完结</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>① 预约咨询二次确认（底部弹窗）：您正在预约 审计（含理账）。确认后，专属顾问将在 24 小时内与您联系并提供报价方案。
+② 预约成功页（顶部：提交预约✓ / 顾问联系 / 报价确认）：已收到您的「审计（含理账）」预约，专属顾问将在 24 小时内与您联系并提供报价方案。可在「我的订单」查看进度。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>公司薪俸税 IR56A&amp;B</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>HKD 556 / ¥ 500</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>约 3 个工作日</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>支付 —— 提交员工薪金 —— 编制 IR56B / A —— 雇主签署提交 IRD —— 完结</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>雇主为员工申报薪金的报税服务，按人头计费、帮填帮交。</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>· 雇主申报员工薪金
 · IR56B（逐员工）+ IR56A（汇总表）
@@ -867,19 +1504,19 @@
 · 税表回执</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>· 公司名称 / 商业登记号 BR
 · 员工名单与薪金明细
 · 申报年度</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>雇主报税表：逐员工一张 IR56B + 汇总 IR56A，按人头计 HKD 556（¥500）/ 人。雇主签署后于 IRD 发出后 1 个月内提交，含帮填帮交。</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 公司名称
@@ -887,70 +1524,70 @@
 · 申报年度（如 2024/25）</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>支付 · 提交员工薪金 · 编制 IR56B / A · 雇主签署提交 IRD · 完结</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>个别人士报税</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>HKD 2,222 / ¥ 2,000</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>约 3 个工作日</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>支付 —— 提交收入资料 —— 编制 BIR60 —— 客户签署提交 IRD —— 完结</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>个人入息 / 薪俸税 BIR60 申报，帮填帮交。</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>· 个人入息 / 薪俸税申报 BIR60
 · 帮填帮交
 · 税表回执</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>· 姓名 / 香港身份证或税务档案号
 · 年度收入资料（薪俸 / 租金等）
 · 可申报的免税额资料</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>个人报税表 BIR60（薪俸 / 租金 / 免税额）；如选个人入息课税另评估。含帮填帮交（不含豁免场景）。</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 姓名
@@ -958,58 +1595,58 @@
 · 申报年度（如 2024/25）</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>支付 · 提交收入资料 · 编制 BIR60 · 客户签署提交 IRD · 完结</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>董事变更</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>HKD 333 / ¥ 300</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>约 5 个工作日</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>支付 —— 提交关键信息 —— 新董事 KYC —— 平台备表 ND2A —— 快递签字确认 —— 递交注册处 —— 完结</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>支付 —— 提交关键信息 —— 新董事 KYC —— 编制 ND2A —— 文件签字确认 —— 递交注册处 —— 完结</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>委任 / 停任董事，备 ND2A / ND4 并递交公司注册处。</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>· 委任 / 停任董事
 · ND2A 变更董事通知书
 · ND4 董事辞职通知书</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>· 公司名称 / 商业登记号 BR
 · 变更类型（委任 / 停任）
@@ -1018,12 +1655,12 @@
 · 新董事 KYC 资料（委任时）</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>您只需提供关键信息（董事姓名 + 证件 + 委任 / 停任及日期）；ND2A / ND4 表格由我们线下准备并快递给您签字确认，签妥回寄后由我们递交公司注册处。委任新董事需完成 KYC 尽调。</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 公司名称
@@ -1035,58 +1672,58 @@
 · 原因 / 生效日期（停任：辞任·去世·其他 · DD/MM/YYYY）</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>支付 · 提交关键信息 · 新董事 KYC · 平台备表 ND2A · 快递签字确认 · 递交注册处 · 完结</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>支付 · 提交关键信息 · 新董事 KYC · 编制 ND2A · 文件签字确认 · 递交注册处 · 完结</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>变更秘书公司</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>HKD 333 / ¥ 300</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>约 5 个工作日</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>支付 —— 确认接任信息 —— 平台备表 ND2A —— 快递签字确认 —— 递交注册处 —— 完结</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>支付 —— 确认接任信息 —— 编制 ND2A —— 文件签字确认 —— 递交注册处 —— 完结</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>将法定公司秘书转由 Leapex 利柏思 接任，备 ND2A 递交。</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>· 最新商业登记证 BR
 · 变更秘书通知书
 · Leapex 利柏思 接任法定秘书</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>· 公司名称 / 商业登记号 BR
 · 现任秘书公司（如有）
@@ -1094,12 +1731,12 @@
 · 董事签字</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>秘书公司即 Leapex 利柏思，表格由我们填写，您只需确认接任并由董事签字。ND2A（秘书部分）线下准备并快递给您签字，签妥回寄后递交注册处；含历史文件交接核对。</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 公司名称
@@ -1108,69 +1745,69 @@
 · 确认由 Leapex 利柏思 接任法定秘书（是 / 否）</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>支付 · 确认接任信息 · 平台备表 ND2A · 快递签字确认 · 递交注册处 · 完结</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>支付 · 确认接任信息 · 编制 ND2A · 文件签字确认 · 递交注册处 · 完结</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>变更注册地址</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>HKD 333 / ¥ 300</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>约 5 个工作日</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>支付 —— 提交关键信息 —— 平台备表 NR1 —— 快递签字确认 —— 递交注册处 —— 完结</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>支付 —— 提交关键信息 —— 编制 NR1 —— 文件签字确认 —— 递交注册处 —— 完结</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>变更公司注册办事处地址，备 NR1 递交公司注册处。</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>· 最新商业登记证 BR
 · 变更地址通知书 NR1</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>· 公司名称 / 商业登记号 BR
 · 新注册地址 或 选用 Leapex 利柏思 地址
 · 生效日期</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>您只需提供关键信息（新注册地址 + 生效日期，或选用 Leapex 利柏思 地址）；NR1 表格由我们线下准备并快递给您签字确认，签妥回寄后由我们递交公司注册处。</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>您只需提供关键信息（新注册地址 + 生效日期，或选用 Leapex 利柏思 地址）；NR1 表格由我们线下编制并安排您文件签字确认，签妥后由我们递交公司注册处。</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 公司名称
@@ -1179,51 +1816,51 @@
 · 生效日期（DD/MM/YYYY）</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>支付 · 提交关键信息 · 平台备表 NR1 · 快递签字确认 · 递交注册处 · 完结</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>支付 · 提交关键信息 · 编制 NR1 · 文件签字确认 · 递交注册处 · 交付新 BR</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>公司更名</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>HKD 1,667 / ¥ 1,500</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>7–10 个工作日；新 BR 约 +2 周</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>支付 —— 提交拟用新名称 —— 人工查名 —— 平台备表 NNC2 + 决议 —— 快递签字确认 —— 递交注册处 —— 完结</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>支付 —— 提交拟用新名称 —— 人工查名 —— 编制 NNC2 + 决议 —— 文件签字确认 —— 递交注册处 —— 完结</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>公司更名，先人工查名再备 NNC2 + 股东特别决议，含新印章。</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>· 拟用新名称查册结果
 · 股东特别决议书
@@ -1232,19 +1869,19 @@
 · 更新印章 ×2</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>· 现公司中 / 英文名 + 商业登记号 BR
 · 拟用新名称（中 / 英）
 · 股东特别决议签署</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>先付费，再由顾问对拟用新名称人工查册（是否可用，含商标风险提示）；NNC2 与股东特别决议书由我们线下准备并快递给您签字确认，签妥回寄后递交注册处。官费 HKD 295，含新印章重制 ×2。</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 现有公司英文名
@@ -1254,51 +1891,51 @@
 · 拟用新中文名（无则填「无」）</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>支付 · 提交拟用新名称 · 人工查名 · 平台备表 NNC2 + 决议 · 快递签字确认 · 递交注册处 · 完结</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>支付 · 提交拟用新名称 · 人工查名 · 编制 NNC2 + 决议 · 文件签字确认 · 递交注册处 · 注册处新 BR</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>股份转让（股东变更）</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>约 5 个工作日</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>支付服务费 —— 提交转让信息 —— 核定作价 + 印花税 —— 受让方 KYC —— 备文书缴印花 —— 快递签字 —— 完结</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>支付服务费 —— 提交转让信息 —— 核定作价 + 印花税 —— 受让方 KYC —— 备文书缴印花 —— 文件签字 —— 完结</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>股东股份转让，核定作价并代缴从价印花税 0.2%。</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>· 转股文书 + 买卖单据
 · 印花税代缴（从价 0.2%）
@@ -1306,7 +1943,7 @@
 · 转让后股东名册 + 新股票</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>· 公司名称 / 商业登记号 BR
 · 转让方 / 受让方信息 + 转让股数
@@ -1315,65 +1952,65 @@
 · 受让方 KYC 资料</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>您提交转让信息 + 估值资料（近 6 月审计报告或近 3 月财务报表）；我们核定作价并代缴从价印花税 0.2%（买卖双方各 0.1% + 每份转让文书定额 HK$5，按对价与资产净值孰高）。受让方须完成 KYC；文书线下快递签字后送 IRD 加盖印花。价格面议（视作价）。</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>您提交转让信息 + 估值资料（近 6 月审计报告或近 3 月财务报表）；我们核定作价并代缴从价印花税 0.2%（买卖双方各 0.1% + 每份转让文书定额 HK$5，按对价与资产净值孰高）。受让方须完成 KYC；文书线下文件签字后送 IRD 加盖印花。价格面议（视作价）。</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>（面议服务：无需在线填写，预约后由顾问对接）</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>支付服务费 · 提交转让信息 · 核定作价 + 印花税 · 受让方 KYC · 备文书缴印花 · 快递签字 · 完结</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>① 预约咨询二次确认（底部弹窗）：你正在预约 股份转让（股东变更）。确认后，专属顾问将在 24 小时内与你联系并提供报价方案。
-② 预约成功页（顶部：提交预约✓ / 顾问联系 / 报价确认）：已收到你的「股份转让（股东变更）」预约，专属顾问将在 24 小时内与你联系并提供报价方案。可在「我的订单」查看进度。</t>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>支付服务费 · 提交转让信息 · 核定作价 + 印花税 · 受让方 KYC · 备文书缴印花 · 文件签字 · 完结</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>① 预约咨询二次确认（底部弹窗）：您正在预约 股份转让（股东变更）。确认后，专属顾问将在 24 小时内与您联系并提供报价方案。
+② 预约成功页（顶部：提交预约✓ / 顾问联系 / 报价确认）：已收到您的「股份转让（股东变更）」预约，专属顾问将在 24 小时内与您联系并提供报价方案。可在「我的订单」查看进度。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>公司注销（撤销注册）</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>约 8 个月（政府审批）</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>支付 —— 提交注销信息 —— 申请 IR1263 —— 备决议 + NDR1 —— 快递签字 —— 递交 + 公告</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>支付 —— 提交注销信息 —— 申请 IR1263 —— 备决议 + NDR1 —— 文件签字 —— 递交 + 公告</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>撤销注册注销公司，办 IR1263 不反对通知书 + NDR1。</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>· 税务局不反对通知书 IR1263
 · 股东特别决议书
 · 撤销注册申请 NDR1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>· 公司名称 / 商业登记号 BR
 · 全体股东同意
@@ -1381,64 +2018,64 @@
 · （如需）清算审计报告</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>撤销注册须全体股东同意、无未偿还债务、停业逾 3 个月；先申请税务局不反对通知书 IR1263（如有欠税须结清，可能需额外清算审计报告）。NDR1 + 决议线下快递签字后递交注册处并宪报公告（异议期约 3 个月）。官费 HKD 270+420，价格面议。</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>撤销注册须全体股东同意、无未偿还债务、停业逾 3 个月；先申请税务局不反对通知书 IR1263（如有欠税须结清，可能需额外清算审计报告）。NDR1 + 决议线下文件签字后递交注册处并宪报公告（异议期约 3 个月）。官费 HKD 270+420，价格面议。</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>（面议服务：无需在线填写，预约后由顾问对接）</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>支付 · 提交注销信息 · 申请 IR1263 · 备决议 + NDR1 · 快递签字 · 递交 + 公告</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>① 预约咨询二次确认（底部弹窗）：你正在预约 公司注销（撤销注册）。确认后，专属顾问将在 24 小时内与你联系并提供报价方案。
-② 预约成功页（顶部：提交预约✓ / 顾问联系 / 报价确认）：已收到你的「公司注销（撤销注册）」预约，专属顾问将在 24 小时内与你联系并提供报价方案。可在「我的订单」查看进度。</t>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>支付 · 提交注销信息 · 申请 IR1263 · 备决议 + NDR1 · 文件签字 · 递交 + 公告</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>① 预约咨询二次确认（底部弹窗）：您正在预约 公司注销（撤销注册）。确认后，专属顾问将在 24 小时内与您联系并提供报价方案。
+② 预约成功页（顶部：提交预约✓ / 顾问联系 / 报价确认）：已收到您的「公司注销（撤销注册）」预约，专属顾问将在 24 小时内与您联系并提供报价方案。可在「我的订单」查看进度。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>商标注册申请</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>HKD 3,311 / ¥ 2,980</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>约 6 个月</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>支付 —— 提交商标信息 —— 递交 IPD —— 审查 + 公告 —— 发证</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>香港知识产权署 IPD 商标注册，每个类别单独申请。</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>· 注册申请表
 · 商标注册证书</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>· 商标名称 / 图样
 · 申请类别 Class（如 9 / 35 / 42）
@@ -1446,12 +2083,12 @@
 · 联系邮箱</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>递交知识产权署 IPD：每个类别单独申请（一个类别 HKD 3,311 / ¥2,980）→ 审查 → 宪报公告（异议期 3 个月）→ 发证。</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 商标名称 / 图样
@@ -1460,69 +2097,69 @@
 · 联系邮箱（name@email.com）</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>支付 · 提交商标信息 · 递交 IPD · 审查 + 公告 · 发证</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>商标注册续期</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>HKD 2,200 / ¥ 1,980</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>约 5 个工作日</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>支付 —— 提交商标编号 —— 递交续期 IPD —— 完结</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>商标每 10 年续期，向 IPD 递交续期申请。</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>· 商标续期申请
 · 续期回执</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>· 商标名称
 · 商标注册编号
 · 续期年度</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>商标每 10 年续期一次；提交商标注册编号后由我们向知识产权署 IPD 递交续期。续期费 HKD 2,200（¥1,980）。</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 商标名称
@@ -1530,70 +2167,70 @@
 · 续期年度</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>支付 · 提交商标编号 · 递交续期 IPD · 完结</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>独立注册地址</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>HKD 6,000 / ¥ 5,400</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>付款后 1–2 个工作日出资料</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>支付 —— 提交公司资料 —— 平台配置地址 —— 出厘印税单 + 水电单 —— 完结</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>独立香港注册地址（不可办公），交付租约 + 厘印税单 + 水电单。</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>· 正规租赁合约
 · 厘印税单（印花税）
 · 物业出具水电单</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>· 公司名称 / 拟注册名称
 · 用途说明
 · 联系人 · 手机</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>独立香港注册地址（不可实体办公），交付租约 + 厘印税单 + 水电单，满足亚马逊等平台地址验证。款项须付至香港公司主体（合规要求）。</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 公司名称 / 拟注册名称
@@ -1602,51 +2239,51 @@
 · 备注（选填）</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>支付 · 提交公司资料 · 平台配置地址 · 出厘印税单 + 水电单 · 完结</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
 ② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+③ 结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。
+④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证。
+⑤ KYC「人工审核中」：顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>工位租赁</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>HKD 3,000 / ¥ 2,500</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>预约后达利对接 · 签约即交付</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>支付 —— 提交需求 —— 生态合作 · 达利对接 —— 签约 —— 交付</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>达利大厦实体工位（可办公），可作注册地址，按月租赁。</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>面议</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>预约后线上或香港实地看工位</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>提交需求 —— 顾问对接 —— 看位 / 报价 —— 签约 —— 交付</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>香港上市公司自持物业实体工位（可办公），可作注册地址，按年租赁。</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>· 正规租赁合约
 · 厘印税单（印花税）
@@ -1654,19 +2291,19 @@
 · 实体工位（可办公）</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>· 公司 / 联系人
 · 工位数量
 · 期望起租日</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>达利大厦实体工位（可办公），交付租约 + 厘印税单 + 水电单，可作注册地址。生态合作：预约后由达利对接、双方签约；按月结算。</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>香港上市公司自持物业实体工位（可办公），交付租约 + 厘印税单 + 水电单，可作注册地址。预约后线上或香港实地看位，由顾问对接、双方签约（按年结算）。</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页字段：
 · 公司名称 / 拟注册名称
@@ -1675,51 +2312,48 @@
 · 备注（选填）</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>支付 · 提交需求 · 生态合作 · 达利对接 · 签约 · 交付</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>① 账单支付页（顶部：下单✓ / 支付·进行中 / 办理）
-② 支付完成页（顶部：下单✓ / 支付✓ / 办理·进行中）
-③ 结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。
-④ 结果页「信息已提交」：办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。
-⑤ KYC「人工审核中」：顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>提交需求 · 顾问对接 · 看位 / 报价 · 签约 · 交付</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>① 预约咨询二次确认（底部弹窗）：您正在预约 工位租赁。确认后，专属顾问将在 24 小时内与您联系并提供报价方案。
+② 预约成功页（顶部：提交预约✓ / 顾问联系 / 报价确认）：已收到您的「工位租赁」预约，专属顾问将在 24 小时内与您联系并提供报价方案。可在「我的订单」查看进度。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>独立办公室租赁</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>面议</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>预约后达利对接 · 看房报价</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>提交需求 —— 生态合作 · 达利对接 —— 看房 / 报价 —— 与达利直签</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>达利大厦独立办公室（可办公），按面积 / 楼层报价。</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>预约后线上或香港实地看办公室</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>提交需求 —— 顾问对接 —— 看房 / 报价 —— 签约</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>香港上市公司一手甲级物业，独立办公室（可办公），按面积 / 楼层报价。</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>· 正规租赁合约
 · 厘印税单（印花税）
@@ -1727,32 +2361,32 @@
 · 独立办公室（可办公）</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>· 公司 / 联系人
 · 面积需求
 · 预算区间</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>达利大厦独立办公室（可办公）。生态合作：预约后由达利对接，客户与达利直签；按面积 / 楼层报价（面议）。</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>香港上市公司自持物业独立办公室（可办公）。预约后线上或香港实地看房、报价、双方签约；按面积 / 楼层报价（面议）。</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>（面议服务：无需在线填写，预约后由顾问对接）</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>提交需求 · 生态合作 · 达利对接 · 看房 / 报价 · 与达利直签</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>① 预约咨询二次确认（底部弹窗）：你正在预约 独立办公室租赁。确认后，专属顾问将在 24 小时内与你联系并提供报价方案。
-② 预约成功页（顶部：提交预约✓ / 顾问联系 / 报价确认）：已收到你的「独立办公室租赁」预约，专属顾问将在 24 小时内与你联系并提供报价方案。可在「我的订单」查看进度。</t>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>提交需求 · 顾问对接 · 看房 / 报价 · 签约</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>① 预约咨询二次确认（底部弹窗）：您正在预约 独立办公室租赁。确认后，专属顾问将在 24 小时内与您联系并提供报价方案。
+② 预约成功页（顶部：提交预约✓ / 顾问联系 / 报价确认）：已收到您的「独立办公室租赁」预约，专属顾问将在 24 小时内与您联系并提供报价方案。可在「我的订单」查看进度。</t>
         </is>
       </c>
     </row>
@@ -1768,7 +2402,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1793,62 +2427,62 @@
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>用户侧业务流程</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>公司资料 —— 成员/董事 —— 组织章程 —— 人工预审</t>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>公司资料 —— 股东/董事 —— 组织章程 —— 人工预审</t>
         </is>
       </c>
     </row>
     <row r="3" ht="120" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>页面 1</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>公司资料</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>标题：公司资料
 · 建议采用的公司名称：拟用公司全名（繁体中文）/ 拟用公司全名（英文）（可只填其一，已复用免费核名记录）
-· 拟经营业务性质：香港标准行业分类 HSIC 下拉选择
-· 公司在香港的注册办事处的建议地址（单选）：填写秘书公司地址（直接采用 Leapex 利柏思 法定秘书注册地址）/ 需要租赁办公室（由顾问对接达利安排独立地址/工位/办公室）
+· 拟经营业务性质：香港标准行业分类 HSIC（点击底部弹窗选择）
+· 公司在香港的注册办事处的建议地址（单选）：填写秘书公司地址（直接采用 Leapex 利柏思 法定秘书注册地址）/ 需要租赁办公室（由顾问对接安排独立地址 / 工位 / 办公室）
 · 公司的联络资料：电邮地址
-· 股本及最初股份持有：股份类别 / 货币单位 / 建议发行股份总数 / 创办成员认购股本总额
-· 底部按钮：暂存 · 下一步·成员/董事</t>
+· 股本及最初股份持有：股份类别（默认普通股）/ 货币单位 / 建议发行股份总数 / 股东认购股本总额
+· 底部按钮：暂存 · 下一步·股东/董事</t>
         </is>
       </c>
     </row>
     <row r="4" ht="135" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>页面 2</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>成员 / 董事</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>标题：创办成员 / 董事（公司秘书由 Leapex 利柏思 内嵌担任，无需填写）
-· 类型：自然人 / 法人团体
-· 身份（可多选）：创办成员 / 董事
-· 身份证件：证件类型（香港身份证 / 护照 / 其他证件）+ 上传证件照片（OCR 自动识别，自动带出姓名、证件号码）
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>股东 / 董事</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>标题：添加股东 / 董事（公司秘书由 Leapex 利柏思 内嵌担任，无需填写）
+· 类型：自然人 / 法人团体（先选类型，再选身份）
+· 身份（可多选）：股东 / 董事
+· 身份证件：证件类型（香港身份证 / 护照 / 其他证件）+ 上传证件照片（OCR 自动识别，自动带出姓名、证件号码）+ 上传手持证件照片（人证一致核验）
 · 通讯地址：香港地址 / 非香港地址（非香港时显示国家/地区，默认中国）
 · 常驻地址：默认勾选「同通讯地址」
 · 联络电邮
@@ -1857,17 +2491,17 @@
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>页面 3</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>组织章程</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>标题：组织章程
 · 样本 A（简化格式·推荐，单一/简单股权适用）/ 样本 B（较完整条款）
@@ -1878,17 +2512,17 @@
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>页面 4</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>人工预审</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>标题：人工预审
 说明：提交后由顾问依 NNC1 表格人工预审；通过后进入业务办理（递交香港公司注册处）。
@@ -1899,55 +2533,55 @@
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>结果页</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>业务办理</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>标题：业务办理中
-人工预审通过后，顾问将线下递交 NNC1 表至香港公司注册处；交表后约 1 周可领取 CI / BR 正本。</t>
+人工预审通过后，顾问将编制 NNC1 表格并安排董事 / 股东文件签字，签妥后递交香港公司注册处；签发 CI + BR 后快递寄出。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>完成页</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>公司注册完成</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>标题：公司注册完成
-TimeLeap Limited 已成功注册，CI 与 BR 已签发，交付物已送达交付物中心。</t>
+TimeLeap Limited 已成功注册，CI 与 BR 已签发，交付物已快递寄出（快递单号 SF1234567890）。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>订单页办理进度</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>支付 · KYC 认证 · 提交注册信息 · 人工预审 · 政府审批 · 交付 CI / BR</t>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>支付 · KYC 认证 · 提交注册信息 · 预审与文件编制 · 文件签字 · 递交注册处 · 交付 CI / BR</t>
         </is>
       </c>
     </row>
@@ -1963,7 +2597,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -1988,52 +2622,52 @@
       </c>
     </row>
     <row r="2" ht="43" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>1 服务详情</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>服务详情页</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>商品名称 · icon · 服务简要介绍 · 服务交付内容 · 办理时效 · 所需材料 · 办理流程 · 详细描述 · 价格（含券后价）
-底部：券后价 / 价格 · 问顾问 · 立即办理</t>
+底部：券后价 / 价格 · 立即办理</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2 下单确认</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>下单确认页</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>服务名称 · 说明 · 原价 / 优惠 / 合计 · 勾选同意服务条款 · 提交订单</t>
         </is>
       </c>
     </row>
     <row r="4" ht="43" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>3 支付</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>账单支付页</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>顶部流程连线：下单 ✓ / 支付 · 进行中 / 办理
 人民币 ¥ / 港币 HK$ 切换 · 应付金额 · 账单号 · 优惠券（有则默认使用）· 银行转账信息 · 上传汇款回单 · 提交回单</t>
@@ -2041,123 +2675,123 @@
       </c>
     </row>
     <row r="5" ht="43" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>4 支付完成</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>支付完成页</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>顶部流程连线：下单 ✓ / 支付 ✓ / 办理 · 进行中
-结果页「支付成功」：已收到你的款项。请继续提交本次办理所需的信息。</t>
+结果页「支付成功」：已收到您的款项。请继续提交本次办理所需的信息。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5 提交办理信息</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>提交办理信息页</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>按各服务「用户填写页 · 表单字段」列示的字段填写（见总览表）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>6 信息已提交</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>结果页</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>办理所需信息已提交。最后一步：完成 KYC 实名认证（香港持牌 TCSP 合规必做）。</t>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>办理所需信息已提交。最后一步：完成 KYC 实名认证。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>7 KYC 认证</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>KYC 认证页</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>AML 合规说明 → 身份认证（证件上传 + 邮箱本人验证）→ 地址证明 → 业务声明 → 提交审核</t>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>AML 合规说明 → 身份认证（证件上传 + 手持证件照片人证一致核验 + 邮箱本人验证）→ 地址证明（水电账单）→ 业务声明 → 提交审核</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>8 人工审核</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>KYC 人工审核中</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>顾问正在依 AMLO 对你的 KYC 资料进行人工审核（约 1 个工作日）。</t>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>顾问正在依 AMLO 对您的 KYC 资料进行人工审核（约 1 个工作日）。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>面议服务·预约</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>预约咨询二次确认弹窗</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>你正在预约 [服务名]。确认后，专属顾问将在 24 小时内与你联系并提供报价方案。（按钮：再想想 / 确认预约）</t>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>您正在预约 [服务名]。确认后，专属顾问将在 24 小时内与您联系并提供报价方案。（按钮：再想想 / 确认预约）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="43" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>面议服务·完成</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>预约成功页</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>顶部：提交预约 ✓ / 顾问联系 / 报价确认
-已收到你的「[服务名]」预约，专属顾问将在 24 小时内与你联系并提供报价方案。</t>
+已收到您的「[服务名]」预约，专属顾问将在 24 小时内与您联系并提供报价方案。</t>
         </is>
       </c>
     </row>
